--- a/Comparison Analysis/Results/Output_monthly_mean_costs-Adjusted.xlsx
+++ b/Comparison Analysis/Results/Output_monthly_mean_costs-Adjusted.xlsx
@@ -387,16 +387,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>102.9305685490057</v>
+        <v>440.3617642796382</v>
       </c>
       <c r="C2">
-        <v>102.931</v>
+        <v>440.362</v>
       </c>
       <c r="D2">
-        <v>101.55</v>
+        <v>434.104</v>
       </c>
       <c r="E2">
-        <v>104.347</v>
+        <v>446.603</v>
       </c>
     </row>
     <row r="3">
@@ -404,16 +404,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>72.04286949873585</v>
+        <v>286.6246039377216</v>
       </c>
       <c r="C3">
-        <v>72.04300000000001</v>
+        <v>286.625</v>
       </c>
       <c r="D3">
-        <v>70.857</v>
+        <v>280.887</v>
       </c>
       <c r="E3">
-        <v>73.15300000000001</v>
+        <v>292.086</v>
       </c>
     </row>
     <row r="4">
@@ -421,16 +421,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>66.31357603678109</v>
+        <v>264.5237456587081</v>
       </c>
       <c r="C4">
-        <v>66.31399999999999</v>
+        <v>264.524</v>
       </c>
       <c r="D4">
-        <v>65.089</v>
+        <v>258.941</v>
       </c>
       <c r="E4">
-        <v>67.56</v>
+        <v>269.848</v>
       </c>
     </row>
     <row r="5">
@@ -438,16 +438,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>54.5070391117053</v>
+        <v>218.4515576150057</v>
       </c>
       <c r="C5">
-        <v>54.507</v>
+        <v>218.452</v>
       </c>
       <c r="D5">
-        <v>53.333</v>
+        <v>213.193</v>
       </c>
       <c r="E5">
-        <v>55.616</v>
+        <v>223.625</v>
       </c>
     </row>
     <row r="6">
@@ -455,16 +455,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>50.15316418349769</v>
+        <v>202.0505032954476</v>
       </c>
       <c r="C6">
-        <v>50.153</v>
+        <v>202.051</v>
       </c>
       <c r="D6">
-        <v>49.069</v>
+        <v>194.128</v>
       </c>
       <c r="E6">
-        <v>51.243</v>
+        <v>210.354</v>
       </c>
     </row>
     <row r="7">
@@ -472,16 +472,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>44.99899853109132</v>
+        <v>175.9000386756104</v>
       </c>
       <c r="C7">
-        <v>44.999</v>
+        <v>175.9</v>
       </c>
       <c r="D7">
-        <v>43.942</v>
+        <v>171.145</v>
       </c>
       <c r="E7">
-        <v>46.008</v>
+        <v>180.403</v>
       </c>
     </row>
     <row r="8">
@@ -489,16 +489,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>43.17871147085134</v>
+        <v>170.8128788696313</v>
       </c>
       <c r="C8">
-        <v>43.179</v>
+        <v>170.813</v>
       </c>
       <c r="D8">
-        <v>42.124</v>
+        <v>166.128</v>
       </c>
       <c r="E8">
-        <v>44.18</v>
+        <v>175.363</v>
       </c>
     </row>
     <row r="9">
@@ -506,16 +506,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>39.13646790822757</v>
+        <v>155.2831138322724</v>
       </c>
       <c r="C9">
-        <v>39.136</v>
+        <v>155.283</v>
       </c>
       <c r="D9">
-        <v>38.181</v>
+        <v>150.881</v>
       </c>
       <c r="E9">
-        <v>40.087</v>
+        <v>159.807</v>
       </c>
     </row>
     <row r="10">
@@ -523,16 +523,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>38.52977404146706</v>
+        <v>151.795278936507</v>
       </c>
       <c r="C10">
-        <v>38.53</v>
+        <v>151.795</v>
       </c>
       <c r="D10">
-        <v>37.509</v>
+        <v>147.381</v>
       </c>
       <c r="E10">
-        <v>39.564</v>
+        <v>156.328</v>
       </c>
     </row>
     <row r="11">
@@ -540,16 +540,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>36.83765658213668</v>
+        <v>146.3719537620178</v>
       </c>
       <c r="C11">
-        <v>36.838</v>
+        <v>146.372</v>
       </c>
       <c r="D11">
-        <v>35.902</v>
+        <v>141.97</v>
       </c>
       <c r="E11">
-        <v>37.754</v>
+        <v>150.749</v>
       </c>
     </row>
     <row r="12">
@@ -557,16 +557,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>34.7137153592008</v>
+        <v>140.1275532327587</v>
       </c>
       <c r="C12">
-        <v>34.714</v>
+        <v>140.128</v>
       </c>
       <c r="D12">
-        <v>33.771</v>
+        <v>135.787</v>
       </c>
       <c r="E12">
-        <v>35.638</v>
+        <v>144.436</v>
       </c>
     </row>
     <row r="13">
@@ -574,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>35.45677966443888</v>
+        <v>141.8307783106809</v>
       </c>
       <c r="C13">
-        <v>35.457</v>
+        <v>141.831</v>
       </c>
       <c r="D13">
-        <v>34.521</v>
+        <v>137.378</v>
       </c>
       <c r="E13">
-        <v>36.424</v>
+        <v>146.37</v>
       </c>
     </row>
     <row r="14">
@@ -591,16 +591,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>32.7982042977835</v>
+        <v>129.001155457226</v>
       </c>
       <c r="C14">
-        <v>32.798</v>
+        <v>129.001</v>
       </c>
       <c r="D14">
-        <v>31.894</v>
+        <v>124.948</v>
       </c>
       <c r="E14">
-        <v>33.661</v>
+        <v>133.198</v>
       </c>
     </row>
     <row r="15">
@@ -608,16 +608,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>32.36236342144208</v>
+        <v>127.7913979331175</v>
       </c>
       <c r="C15">
-        <v>32.362</v>
+        <v>127.791</v>
       </c>
       <c r="D15">
-        <v>31.445</v>
+        <v>123.874</v>
       </c>
       <c r="E15">
-        <v>33.303</v>
+        <v>131.918</v>
       </c>
     </row>
     <row r="16">
@@ -625,16 +625,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>30.52648522030822</v>
+        <v>119.9110311371721</v>
       </c>
       <c r="C16">
-        <v>30.526</v>
+        <v>119.911</v>
       </c>
       <c r="D16">
-        <v>29.646</v>
+        <v>115.756</v>
       </c>
       <c r="E16">
-        <v>31.377</v>
+        <v>124.138</v>
       </c>
     </row>
     <row r="17">
@@ -642,16 +642,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>29.59164402760683</v>
+        <v>115.8818066551589</v>
       </c>
       <c r="C17">
-        <v>29.592</v>
+        <v>115.882</v>
       </c>
       <c r="D17">
-        <v>28.733</v>
+        <v>111.976</v>
       </c>
       <c r="E17">
-        <v>30.455</v>
+        <v>119.795</v>
       </c>
     </row>
     <row r="18">
@@ -659,16 +659,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>28.02754795792075</v>
+        <v>112.193846381987</v>
       </c>
       <c r="C18">
-        <v>28.028</v>
+        <v>112.194</v>
       </c>
       <c r="D18">
-        <v>27.255</v>
+        <v>108.29</v>
       </c>
       <c r="E18">
-        <v>28.818</v>
+        <v>115.954</v>
       </c>
     </row>
     <row r="19">
@@ -676,16 +676,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>27.55244949948768</v>
+        <v>109.7711173902116</v>
       </c>
       <c r="C19">
-        <v>27.552</v>
+        <v>109.771</v>
       </c>
       <c r="D19">
-        <v>26.724</v>
+        <v>105.823</v>
       </c>
       <c r="E19">
-        <v>28.417</v>
+        <v>113.753</v>
       </c>
     </row>
     <row r="20">
@@ -693,16 +693,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>27.14468553155065</v>
+        <v>107.9707324220096</v>
       </c>
       <c r="C20">
-        <v>27.145</v>
+        <v>107.971</v>
       </c>
       <c r="D20">
-        <v>26.298</v>
+        <v>104.313</v>
       </c>
       <c r="E20">
-        <v>27.996</v>
+        <v>111.808</v>
       </c>
     </row>
     <row r="21">
@@ -710,16 +710,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>25.15960007541148</v>
+        <v>99.34847080978014</v>
       </c>
       <c r="C21">
-        <v>25.16</v>
+        <v>99.348</v>
       </c>
       <c r="D21">
-        <v>24.354</v>
+        <v>95.768</v>
       </c>
       <c r="E21">
-        <v>25.969</v>
+        <v>103.017</v>
       </c>
     </row>
     <row r="22">
@@ -727,16 +727,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>25.82929556318664</v>
+        <v>102.0518621891034</v>
       </c>
       <c r="C22">
-        <v>25.829</v>
+        <v>102.052</v>
       </c>
       <c r="D22">
-        <v>24.976</v>
+        <v>98.172</v>
       </c>
       <c r="E22">
-        <v>26.69</v>
+        <v>106.086</v>
       </c>
     </row>
     <row r="23">
@@ -744,16 +744,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>23.41703385294085</v>
+        <v>94.13905826983509</v>
       </c>
       <c r="C23">
-        <v>23.417</v>
+        <v>94.139</v>
       </c>
       <c r="D23">
-        <v>22.672</v>
+        <v>90.52800000000001</v>
       </c>
       <c r="E23">
-        <v>24.174</v>
+        <v>97.711</v>
       </c>
     </row>
     <row r="24">
@@ -761,16 +761,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>23.79645801896145</v>
+        <v>95.2219991848567</v>
       </c>
       <c r="C24">
-        <v>23.796</v>
+        <v>95.22199999999999</v>
       </c>
       <c r="D24">
-        <v>22.96</v>
+        <v>91.709</v>
       </c>
       <c r="E24">
-        <v>24.608</v>
+        <v>98.702</v>
       </c>
     </row>
     <row r="25">
@@ -778,16 +778,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>22.04638042408187</v>
+        <v>87.12199913493338</v>
       </c>
       <c r="C25">
-        <v>22.046</v>
+        <v>87.122</v>
       </c>
       <c r="D25">
-        <v>21.311</v>
+        <v>83.71299999999999</v>
       </c>
       <c r="E25">
-        <v>22.778</v>
+        <v>90.608</v>
       </c>
     </row>
   </sheetData>
@@ -832,16 +832,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>107.8430566442464</v>
+        <v>143.7144854834236</v>
       </c>
       <c r="C2">
-        <v>107.843</v>
+        <v>143.714</v>
       </c>
       <c r="D2">
-        <v>106.075</v>
+        <v>141.226</v>
       </c>
       <c r="E2">
-        <v>109.57</v>
+        <v>146.104</v>
       </c>
     </row>
     <row r="3">
@@ -849,16 +849,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>73.67915704703891</v>
+        <v>97.91835948667396</v>
       </c>
       <c r="C3">
-        <v>73.679</v>
+        <v>97.91800000000001</v>
       </c>
       <c r="D3">
-        <v>72.324</v>
+        <v>95.754</v>
       </c>
       <c r="E3">
-        <v>75.075</v>
+        <v>99.976</v>
       </c>
     </row>
     <row r="4">
@@ -866,16 +866,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>67.98267898191489</v>
+        <v>90.53125718969372</v>
       </c>
       <c r="C4">
-        <v>67.983</v>
+        <v>90.53100000000001</v>
       </c>
       <c r="D4">
-        <v>66.517</v>
+        <v>88.36199999999999</v>
       </c>
       <c r="E4">
-        <v>69.417</v>
+        <v>92.685</v>
       </c>
     </row>
     <row r="5">
@@ -883,16 +883,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>55.487651019738</v>
+        <v>73.90900735478594</v>
       </c>
       <c r="C5">
-        <v>55.488</v>
+        <v>73.90900000000001</v>
       </c>
       <c r="D5">
-        <v>54.241</v>
+        <v>72.09099999999999</v>
       </c>
       <c r="E5">
-        <v>56.747</v>
+        <v>75.715</v>
       </c>
     </row>
     <row r="6">
@@ -900,16 +900,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>50.19644920966601</v>
+        <v>66.96823888821348</v>
       </c>
       <c r="C6">
-        <v>50.196</v>
+        <v>66.968</v>
       </c>
       <c r="D6">
-        <v>48.913</v>
+        <v>65.22199999999999</v>
       </c>
       <c r="E6">
-        <v>51.493</v>
+        <v>68.60899999999999</v>
       </c>
     </row>
     <row r="7">
@@ -917,16 +917,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>45.36580870485795</v>
+        <v>60.23804756612569</v>
       </c>
       <c r="C7">
-        <v>45.366</v>
+        <v>60.238</v>
       </c>
       <c r="D7">
-        <v>44.217</v>
+        <v>58.494</v>
       </c>
       <c r="E7">
-        <v>46.539</v>
+        <v>61.914</v>
       </c>
     </row>
     <row r="8">
@@ -934,16 +934,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>43.58758364836262</v>
+        <v>58.19863611664969</v>
       </c>
       <c r="C8">
-        <v>43.588</v>
+        <v>58.199</v>
       </c>
       <c r="D8">
-        <v>42.428</v>
+        <v>56.474</v>
       </c>
       <c r="E8">
-        <v>44.723</v>
+        <v>59.948</v>
       </c>
     </row>
     <row r="9">
@@ -951,16 +951,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>39.37621788766813</v>
+        <v>52.74614870663845</v>
       </c>
       <c r="C9">
-        <v>39.376</v>
+        <v>52.746</v>
       </c>
       <c r="D9">
-        <v>38.299</v>
+        <v>51.212</v>
       </c>
       <c r="E9">
-        <v>40.521</v>
+        <v>54.213</v>
       </c>
     </row>
     <row r="10">
@@ -968,16 +968,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>39.12684050637654</v>
+        <v>51.76413353852964</v>
       </c>
       <c r="C10">
-        <v>39.127</v>
+        <v>51.764</v>
       </c>
       <c r="D10">
-        <v>38.021</v>
+        <v>50.273</v>
       </c>
       <c r="E10">
-        <v>40.232</v>
+        <v>53.332</v>
       </c>
     </row>
     <row r="11">
@@ -985,16 +985,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>37.51529230689903</v>
+        <v>50.36745151622979</v>
       </c>
       <c r="C11">
-        <v>37.515</v>
+        <v>50.367</v>
       </c>
       <c r="D11">
-        <v>36.432</v>
+        <v>48.853</v>
       </c>
       <c r="E11">
-        <v>38.584</v>
+        <v>51.923</v>
       </c>
     </row>
     <row r="12">
@@ -1002,16 +1002,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>35.09366901384218</v>
+        <v>46.79366347805382</v>
       </c>
       <c r="C12">
-        <v>35.094</v>
+        <v>46.794</v>
       </c>
       <c r="D12">
-        <v>34.034</v>
+        <v>45.322</v>
       </c>
       <c r="E12">
-        <v>36.171</v>
+        <v>48.247</v>
       </c>
     </row>
     <row r="13">
@@ -1019,16 +1019,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>35.90562436443723</v>
+        <v>48.28312783914052</v>
       </c>
       <c r="C13">
-        <v>35.906</v>
+        <v>48.283</v>
       </c>
       <c r="D13">
-        <v>34.874</v>
+        <v>46.687</v>
       </c>
       <c r="E13">
-        <v>36.962</v>
+        <v>49.849</v>
       </c>
     </row>
     <row r="14">
@@ -1036,16 +1036,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>33.00314809511802</v>
+        <v>43.91374972859748</v>
       </c>
       <c r="C14">
-        <v>33.003</v>
+        <v>43.914</v>
       </c>
       <c r="D14">
-        <v>32.004</v>
+        <v>42.522</v>
       </c>
       <c r="E14">
-        <v>33.981</v>
+        <v>45.376</v>
       </c>
     </row>
     <row r="15">
@@ -1053,16 +1053,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>32.85118066732093</v>
+        <v>43.74588915506916</v>
       </c>
       <c r="C15">
-        <v>32.851</v>
+        <v>43.746</v>
       </c>
       <c r="D15">
-        <v>31.829</v>
+        <v>42.208</v>
       </c>
       <c r="E15">
-        <v>33.898</v>
+        <v>45.207</v>
       </c>
     </row>
     <row r="16">
@@ -1070,16 +1070,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>31.34510361512118</v>
+        <v>41.81951425459541</v>
       </c>
       <c r="C16">
-        <v>31.345</v>
+        <v>41.82</v>
       </c>
       <c r="D16">
-        <v>30.288</v>
+        <v>40.417</v>
       </c>
       <c r="E16">
-        <v>32.358</v>
+        <v>43.232</v>
       </c>
     </row>
     <row r="17">
@@ -1087,16 +1087,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>29.99260749910851</v>
+        <v>39.85618252648835</v>
       </c>
       <c r="C17">
-        <v>29.993</v>
+        <v>39.856</v>
       </c>
       <c r="D17">
-        <v>28.934</v>
+        <v>38.391</v>
       </c>
       <c r="E17">
-        <v>31.015</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="18">
@@ -1104,16 +1104,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>28.26546445251643</v>
+        <v>37.90632527607676</v>
       </c>
       <c r="C18">
-        <v>28.265</v>
+        <v>37.906</v>
       </c>
       <c r="D18">
-        <v>27.355</v>
+        <v>36.6</v>
       </c>
       <c r="E18">
-        <v>29.186</v>
+        <v>39.209</v>
       </c>
     </row>
     <row r="19">
@@ -1121,16 +1121,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>27.86072196154047</v>
+        <v>37.14939289344017</v>
       </c>
       <c r="C19">
-        <v>27.861</v>
+        <v>37.149</v>
       </c>
       <c r="D19">
-        <v>26.943</v>
+        <v>35.742</v>
       </c>
       <c r="E19">
-        <v>28.818</v>
+        <v>38.593</v>
       </c>
     </row>
     <row r="20">
@@ -1138,16 +1138,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>27.38066606134837</v>
+        <v>37.03160365043783</v>
       </c>
       <c r="C20">
-        <v>27.381</v>
+        <v>37.032</v>
       </c>
       <c r="D20">
-        <v>26.418</v>
+        <v>35.749</v>
       </c>
       <c r="E20">
-        <v>28.382</v>
+        <v>38.351</v>
       </c>
     </row>
     <row r="21">
@@ -1155,16 +1155,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>25.43697462656533</v>
+        <v>34.13625971841934</v>
       </c>
       <c r="C21">
-        <v>25.437</v>
+        <v>34.136</v>
       </c>
       <c r="D21">
-        <v>24.529</v>
+        <v>32.74</v>
       </c>
       <c r="E21">
-        <v>26.365</v>
+        <v>35.481</v>
       </c>
     </row>
     <row r="22">
@@ -1172,16 +1172,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>26.22347496520407</v>
+        <v>35.30507270191694</v>
       </c>
       <c r="C22">
-        <v>26.223</v>
+        <v>35.305</v>
       </c>
       <c r="D22">
-        <v>25.251</v>
+        <v>33.877</v>
       </c>
       <c r="E22">
-        <v>27.206</v>
+        <v>36.723</v>
       </c>
     </row>
     <row r="23">
@@ -1189,16 +1189,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>23.57760119763544</v>
+        <v>31.97647626260139</v>
       </c>
       <c r="C23">
-        <v>23.578</v>
+        <v>31.976</v>
       </c>
       <c r="D23">
-        <v>22.652</v>
+        <v>30.681</v>
       </c>
       <c r="E23">
-        <v>24.456</v>
+        <v>33.272</v>
       </c>
     </row>
     <row r="24">
@@ -1206,16 +1206,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>24.27030491360938</v>
+        <v>32.30133219148031</v>
       </c>
       <c r="C24">
-        <v>24.27</v>
+        <v>32.301</v>
       </c>
       <c r="D24">
-        <v>23.354</v>
+        <v>31.01</v>
       </c>
       <c r="E24">
-        <v>25.213</v>
+        <v>33.557</v>
       </c>
     </row>
     <row r="25">
@@ -1223,16 +1223,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>22.81856252000242</v>
+        <v>31.06264124771286</v>
       </c>
       <c r="C25">
-        <v>22.819</v>
+        <v>31.063</v>
       </c>
       <c r="D25">
-        <v>21.898</v>
+        <v>29.752</v>
       </c>
       <c r="E25">
-        <v>23.737</v>
+        <v>32.322</v>
       </c>
     </row>
   </sheetData>
